--- a/史料统计.xlsx
+++ b/史料统计.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\留声南洋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA9C87D-0F89-4EF5-8251-5788CABBA082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABBCA9C-1189-4B2B-BC1A-DE4C29E54DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,9 +146,6 @@
     <t>联合早报 (Lianhe Zaobao), 26 January 1985, Page 61</t>
   </si>
   <si>
-    <t>南洋商报 (Nanyang Siang Pau), 5 September 1938</t>
-  </si>
-  <si>
     <t>南洋商报 (Nanyang Siang Pau), 11 December 1940, Page 6</t>
   </si>
   <si>
@@ -161,282 +158,287 @@
     <t>南洋商报 (Nanyang Siang Pau), 25 July 1977, Page 9</t>
   </si>
   <si>
+    <t>南洋商报 (Nanyang Siang Pau), 30 December 1974, Page 3</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 2 June 1972, Page 24</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 26 May 1972, Page 27</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d2</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d3</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d4</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263602</t>
+  </si>
+  <si>
+    <t>冯伊湄</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/1242abf3-a085-4ed7-a1d7-f956461dc48a</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/1242abf3-a085-4ed7-a1d7-f956461dc48a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>联合晚报</t>
+  </si>
+  <si>
+    <t>联合晚报</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>联合早报</t>
+  </si>
+  <si>
+    <t>申报</t>
+  </si>
+  <si>
+    <t>联合晚报 (Lianhe Wanbao), 9 September 1987, Page 14</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 11 June 1999, Page 10</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 19 September 1983, Page 19</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 19 September 1983, Page 28</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 22 September 1983, Page 28</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 26 September 1983, Page 18</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 27 February 2000, Page 46</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 10 October 1979, Page 20</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 25 January 1975, Page 15</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 28 January 1975, Page 21</t>
+  </si>
+  <si>
+    <t>新明日报 (Xin Ming Ri Bao), 8 February 1987, Page 11</t>
+  </si>
+  <si>
+    <t>新明日报 (Xin Ming Ri Bao), 18 July 1973, Page 8</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 7 June 1982, Page 32</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 8 February 1982, Page 28</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 8 March 1982, Page 28</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 27 February 1939, Page 10</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 30 September 1980, Page 32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大公报香港版, 2 June 1940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王映霞</t>
+  </si>
+  <si>
+    <t>大公报香港版</t>
+  </si>
+  <si>
+    <t>新明日报</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263603</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263604</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/d0d88e36-15e2-4f38-a49e-6d57008fa959</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/d0d88e36-15e2-4f38-a49e-6d57008fa960</t>
+  </si>
+  <si>
+    <t>https://tk.cepiec.com.cn/tknewsc/tknewskm?.779b009F8000010000000000420100F0000000^^tk19406001@1577992971@20hk3003000200011381669a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 24 August 1940, Page 7</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 23 October 1940, Page 13</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 22 August 1940, Page 6</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 20 October 1940, Page 11</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 19 August 1940, Page 13</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 16 July 1940, Page 31</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 15 August 1940, Page 6</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 10 February 1941, Page 9</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 2 October 1940, Page 7</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 1 October 1939, Page 5</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 23 August 1995, Page 34</t>
+  </si>
+  <si>
+    <t>联合晚报 (Lianhe Wanbao), 28 March 1994, Page 19</t>
+  </si>
+  <si>
+    <t>联合晚报 (Lianhe Wanbao), 9 April 1984, Page 2</t>
+  </si>
+  <si>
+    <t>联合晚报 (Lianhe Wanbao), 2 April 1994, Page 23</t>
+  </si>
+  <si>
+    <t>联合晚报 (Lianhe Wanbao), 1 April 1994, Page 21</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 30 September 1939, Page 3, Afternoon Edition</t>
+  </si>
+  <si>
+    <t>大公报香港版, 9 June 1940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 1 July 1941, Page 11</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 7 January 1954, Page 4</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 7 May 1940, Page 10</t>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 15 February 1941, Page 11</t>
+  </si>
+  <si>
+    <t>王莹</t>
+  </si>
+  <si>
+    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263605</t>
+  </si>
+  <si>
+    <t>https://tk.cepiec.com.cn/tknewsc/tknewskm?.3aac08C80E0500000104000F00003^kk9006@@645898192609041ht^0000030100200000010006D006d9f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>联合晚报 (Lianhe Wanbao), 10 April 1994, Page 21</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 12 October 1997, Page 74</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 14 November 1984, Page 39</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 20 October 1996, Page 52</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 23 July 1987, Page 34</t>
+  </si>
+  <si>
+    <t>联合早报 (Lianhe Zaobao), 23 March 1985, Page 43</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 7 March 1937, Page 14</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 9 July 1941, Page 19</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 23 August 1941, Page 6</t>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 30 October 1946, Page 6</t>
+  </si>
+  <si>
+    <t>大公报上海版, 2 December 1945</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大公晚报, 3 October 1945</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>申报, 5 December 1945</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新华日报, 4 October 1945</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大公报上海版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大公晚报</t>
+  </si>
+  <si>
+    <t>新华日报</t>
+  </si>
+  <si>
+    <t>沈兹九</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出版时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>南洋商报 (Nanyang Siang Pau), 27 March 1940, Page 15</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 30 December 1974, Page 3</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 2 June 1972, Page 24</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 26 May 1972, Page 27</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d2</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d3</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/40c1c70e-0d00-4c06-86ff-ba27de2d83d4</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263601</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263602</t>
-  </si>
-  <si>
-    <t>冯伊湄</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/1242abf3-a085-4ed7-a1d7-f956461dc48a</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/1242abf3-a085-4ed7-a1d7-f956461dc48a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>联合晚报</t>
-  </si>
-  <si>
-    <t>联合晚报</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>联合早报</t>
-  </si>
-  <si>
-    <t>申报</t>
-  </si>
-  <si>
-    <t>联合晚报 (Lianhe Wanbao), 9 September 1987, Page 14</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 11 June 1999, Page 10</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 19 September 1983, Page 19</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 19 September 1983, Page 28</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 22 September 1983, Page 28</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 26 September 1983, Page 18</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 27 February 2000, Page 46</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 10 October 1979, Page 20</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 25 January 1975, Page 15</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 28 January 1975, Page 21</t>
-  </si>
-  <si>
-    <t>新明日报 (Xin Ming Ri Bao), 8 February 1987, Page 11</t>
-  </si>
-  <si>
-    <t>新明日报 (Xin Ming Ri Bao), 18 July 1973, Page 8</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 7 June 1982, Page 32</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 8 February 1982, Page 28</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 8 March 1982, Page 28</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 27 February 1939, Page 10</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 30 September 1980, Page 32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 5 May 1982</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大公报香港版, 2 June 1940</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王映霞</t>
-  </si>
-  <si>
-    <t>大公报香港版</t>
-  </si>
-  <si>
-    <t>新明日报</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263603</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263604</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/d0d88e36-15e2-4f38-a49e-6d57008fa959</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/d0d88e36-15e2-4f38-a49e-6d57008fa960</t>
-  </si>
-  <si>
-    <t>https://tk.cepiec.com.cn/tknewsc/tknewskm?.779b009F8000010000000000420100F0000000^^tk19406001@1577992971@20hk3003000200011381669a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 24 August 1940, Page 7</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 23 October 1940, Page 13</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 22 August 1940, Page 6</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 20 October 1940, Page 11</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 19 August 1940, Page 13</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 16 July 1940, Page 31</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 15 August 1940, Page 6</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 10 February 1941, Page 9</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 2 October 1940, Page 7</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 1 October 1939, Page 5</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 23 August 1995, Page 34</t>
-  </si>
-  <si>
-    <t>联合晚报 (Lianhe Wanbao), 28 March 1994, Page 19</t>
-  </si>
-  <si>
-    <t>联合晚报 (Lianhe Wanbao), 9 April 1984, Page 2</t>
-  </si>
-  <si>
-    <t>联合晚报 (Lianhe Wanbao), 2 April 1994, Page 23</t>
-  </si>
-  <si>
-    <t>联合晚报 (Lianhe Wanbao), 1 April 1994, Page 21</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 30 September 1939, Page 3, Afternoon Edition</t>
-  </si>
-  <si>
-    <t>大公报香港版, 9 June 1940</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 1 July 1941, Page 11</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 7 January 1954, Page 4</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 7 May 1940, Page 10</t>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 15 February 1941, Page 11</t>
-  </si>
-  <si>
-    <t>王莹</t>
-  </si>
-  <si>
-    <t>https://eresources.nlb.gov.sg/newspapers/browse/5fde724d-1a70-43ae-bb42-2638c9263605</t>
-  </si>
-  <si>
-    <t>https://tk.cepiec.com.cn/tknewsc/tknewskm?.3aac08C80E0500000104000F00003^kk9006@@645898192609041ht^0000030100200000010006D006d9f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>联合晚报 (Lianhe Wanbao), 10 April 1994, Page 21</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 12 October 1997, Page 74</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 14 November 1984, Page 39</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 20 October 1996, Page 52</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 23 July 1987, Page 34</t>
-  </si>
-  <si>
-    <t>联合早报 (Lianhe Zaobao), 23 March 1985, Page 43</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 7 March 1937, Page 14</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 9 July 1941, Page 19</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 23 August 1941, Page 6</t>
-  </si>
-  <si>
-    <t>南洋商报 (Nanyang Siang Pau), 30 October 1946, Page 6</t>
-  </si>
-  <si>
-    <t>大公报上海版, 2 December 1945</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大公晚报, 3 October 1945</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>申报, 5 December 1945</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新华日报, 4 October 1945</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大公报上海版</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大公晚报</t>
-  </si>
-  <si>
-    <t>新华日报</t>
-  </si>
-  <si>
-    <t>沈兹九</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出版时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 5 September 1938,Page 14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星洲日报 (Sin Chew Jit Poh), 5 May 1982,Page31</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -842,7 +844,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>20</v>
@@ -1109,7 +1111,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1120,13 +1122,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="E2" s="7">
         <v>14128</v>
@@ -1140,13 +1142,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="E3" s="7">
         <v>14697</v>
@@ -1160,13 +1162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="7">
         <v>14956</v>
@@ -1180,19 +1182,19 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" s="7">
         <v>26445</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1200,19 +1202,19 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="7">
         <v>26452</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1220,13 +1222,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7" s="7">
         <v>27393</v>
@@ -1240,13 +1242,13 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7">
         <v>28319</v>
@@ -1260,13 +1262,13 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="7">
         <v>28331</v>
@@ -1280,13 +1282,13 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="7">
         <v>29632</v>
@@ -1300,10 +1302,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1312,7 +1314,7 @@
         <v>30790</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1320,10 +1322,10 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -1332,7 +1334,7 @@
         <v>31073</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1340,10 +1342,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
@@ -1352,7 +1354,7 @@
         <v>31851</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1396,7 +1398,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1407,19 +1409,19 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" s="7">
         <v>14303</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1427,19 +1429,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E3" s="7">
         <v>14764</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1447,19 +1449,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E4" s="7">
         <v>26863</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1467,13 +1469,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" s="7">
         <v>27419</v>
@@ -1487,13 +1489,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" s="7">
         <v>27422</v>
@@ -1507,13 +1509,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" s="7">
         <v>29138</v>
@@ -1527,19 +1529,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E8" s="7">
         <v>29494</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1547,19 +1549,19 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" s="7">
         <v>29990</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1567,19 +1569,19 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" s="7">
         <v>30018</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1587,19 +1589,19 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="E11" s="7">
         <v>30076</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1607,19 +1609,19 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E12" s="7">
         <v>30109</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1627,19 +1629,19 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13" s="7">
         <v>30578</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1647,19 +1649,19 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7">
         <v>30578</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1667,19 +1669,19 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E15" s="7">
         <v>30581</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1687,19 +1689,19 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" s="7">
         <v>30585</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1707,19 +1709,19 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E17" s="7">
         <v>31816</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1727,19 +1729,19 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E18" s="7">
         <v>32029</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1747,19 +1749,19 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E19" s="7">
         <v>36322</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1767,19 +1769,19 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" s="7">
         <v>36583</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1827,7 +1829,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1838,19 +1840,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E2" s="6">
         <v>14518</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1858,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E3" s="6">
         <v>14519</v>
@@ -1878,19 +1880,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E4" s="6">
         <v>14738</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1898,19 +1900,19 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E5" s="6">
         <v>14771</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1918,13 +1920,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E6" s="6">
         <v>14808</v>
@@ -1938,13 +1940,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7" s="6">
         <v>14838</v>
@@ -1958,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E8" s="6">
         <v>14842</v>
@@ -1978,13 +1980,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E9" s="6">
         <v>14845</v>
@@ -1998,13 +2000,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E10" s="6">
         <v>14847</v>
@@ -2018,13 +2020,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E11" s="6">
         <v>14886</v>
@@ -2038,13 +2040,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E12" s="6">
         <v>14904</v>
@@ -2058,13 +2060,13 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E13" s="6">
         <v>14907</v>
@@ -2078,13 +2080,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E14" s="6">
         <v>15017</v>
@@ -2098,19 +2100,19 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E15" s="6">
         <v>15022</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2118,19 +2120,19 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E16" s="6">
         <v>15158</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2138,19 +2140,19 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E17" s="6">
         <v>19731</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2158,19 +2160,19 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E18" s="6">
         <v>30781</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2178,19 +2180,19 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E19" s="6">
         <v>34421</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2198,19 +2200,19 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E20" s="6">
         <v>34425</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2218,19 +2220,19 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E21" s="6">
         <v>34426</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2238,19 +2240,19 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E22" s="6">
         <v>34934</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2294,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -2303,13 +2305,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E2" s="6">
         <v>13581</v>
@@ -2323,13 +2325,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E3" s="6">
         <v>15166</v>
@@ -2343,13 +2345,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E4" s="6">
         <v>15211</v>
@@ -2363,13 +2365,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E5" s="6">
         <v>16713</v>
@@ -2380,13 +2382,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E6" s="6">
         <v>16714</v>
@@ -2397,13 +2399,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E7" s="6">
         <v>16773</v>
@@ -2414,13 +2416,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E8" s="6">
         <v>16776</v>
@@ -2431,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E9" s="6">
         <v>17105</v>
@@ -2451,19 +2453,19 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E10" s="6">
         <v>31000</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2471,19 +2473,19 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E11" s="6">
         <v>31129</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2491,19 +2493,19 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E12" s="6">
         <v>31981</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2511,19 +2513,19 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E13" s="6">
         <v>34434</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2531,19 +2533,19 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E14" s="6">
         <v>35358</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2551,19 +2553,19 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E15" s="6">
         <v>35715</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/史料统计.xlsx
+++ b/史料统计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\留声南洋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABBCA9C-1189-4B2B-BC1A-DE4C29E54DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8724E3-01A8-40CF-8476-E490A9AFF0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="莹姿" sheetId="1" r:id="rId1"/>
@@ -434,11 +434,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>南洋商报 (Nanyang Siang Pau), 5 September 1938,Page 14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星洲日报 (Sin Chew Jit Poh), 5 May 1982,Page31</t>
+    <t>星洲日报 (Sin Chew Jit Poh), 5 May 1982，Page31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南洋商报 (Nanyang Siang Pau), 5 September 1938，Page14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1128,7 +1128,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E2" s="7">
         <v>14128</v>
@@ -1595,7 +1595,7 @@
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E11" s="7">
         <v>30076</v>
